--- a/data/sars/alaska/tables/Alaska_2009_Appendix2.xlsx
+++ b/data/sars/alaska/tables/Alaska_2009_Appendix2.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/alaska/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B60928C-23AF-544C-B3D3-541BC5BAE710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53CBB976-CA56-D14F-AAFF-EFC855EC460F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="16980" windowHeight="19820" xr2:uid="{96A13700-2429-4246-A404-86EBBE95C8D2}"/>
   </bookViews>
   <sheets>
     <sheet name="tabula-Alaska_2009_Appendix2" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="78">
   <si>
     <t>Alaska</t>
   </si>
@@ -97,9 +110,6 @@
     <t>W. N. Pacific</t>
   </si>
   <si>
-    <t>2.6/2.0</t>
-  </si>
-  <si>
     <t>CNP - entire stock</t>
   </si>
   <si>
@@ -133,9 +143,6 @@
     <t>Ribbon seal</t>
   </si>
   <si>
-    <t>49,000_x000D_(provisional)</t>
-  </si>
-  <si>
     <t>Ringed seal</t>
   </si>
   <si>
@@ -154,9 +161,6 @@
     <t>E. U. S.</t>
   </si>
   <si>
-    <t>45,095-_x000D_55,832</t>
-  </si>
-  <si>
     <t>W. U. S.</t>
   </si>
   <si>
@@ -251,6 +255,18 @@
   </si>
   <si>
     <t>comments</t>
+  </si>
+  <si>
+    <t>n_est_notes</t>
+  </si>
+  <si>
+    <t>provisional</t>
+  </si>
+  <si>
+    <t>45,095-55,832</t>
+  </si>
+  <si>
+    <t>pbr_notes</t>
   </si>
 </sst>
 </file>
@@ -1129,64 +1145,72 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18281ADD-1771-3845-B0AA-B7D49286D42F}">
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:Q38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.33203125" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="10.83203125" style="1"/>
+    <col min="3" max="3" width="8.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -1194,32 +1218,32 @@
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="1">
+      <c r="F2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1">
         <v>0.04</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2" s="1">
         <v>0.5</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0</v>
-      </c>
-      <c r="L2" s="1">
-        <v>0</v>
+      <c r="K2" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="M2" s="1">
         <v>0</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="1">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1229,32 +1253,32 @@
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="1">
+      <c r="F3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1">
         <v>0.12</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
         <v>0.5</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="1">
-        <v>1</v>
-      </c>
-      <c r="L3" s="2">
+      <c r="K3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" s="1">
+        <v>1</v>
+      </c>
+      <c r="N3" s="2">
         <v>6788</v>
       </c>
-      <c r="M3" s="2">
+      <c r="O3" s="2">
         <v>6789</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1264,41 +1288,42 @@
       <c r="C4" s="2">
         <v>39258</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="2"/>
+      <c r="E4" s="1">
         <v>0.23</v>
       </c>
-      <c r="E4" s="2">
+      <c r="F4" s="2">
         <v>32453</v>
       </c>
-      <c r="F4" s="2">
+      <c r="G4" s="2">
         <v>14</v>
       </c>
-      <c r="G4" s="1">
+      <c r="H4" s="1">
         <v>1992</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
         <v>0.04</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4" s="1">
         <v>0.5</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K4" s="1">
-        <v>0</v>
-      </c>
-      <c r="L4" s="1">
+      <c r="M4" s="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1">
         <v>139</v>
       </c>
-      <c r="M4" s="1">
+      <c r="O4" s="1">
         <v>139</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1308,41 +1333,42 @@
       <c r="C5" s="2">
         <v>3710</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="D5" s="2"/>
+      <c r="E5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
         <v>3710</v>
       </c>
-      <c r="F5" s="2">
+      <c r="G5" s="2">
         <v>17</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <v>1991</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>0.04</v>
       </c>
-      <c r="I5" s="1">
-        <v>1</v>
-      </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="1">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="1">
-        <v>0</v>
-      </c>
-      <c r="L5" s="1">
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
         <v>59</v>
       </c>
-      <c r="M5" s="1">
+      <c r="O5" s="1">
         <v>59</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="P5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1352,41 +1378,42 @@
       <c r="C6" s="2">
         <v>18142</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="2"/>
+      <c r="E6" s="1">
         <v>0.24</v>
       </c>
-      <c r="E6" s="2">
+      <c r="F6" s="2">
         <v>14898</v>
       </c>
-      <c r="F6" s="2">
+      <c r="G6" s="2">
         <v>8</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>2000</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <v>0.04</v>
       </c>
-      <c r="I6" s="1">
-        <v>1</v>
-      </c>
       <c r="J6" s="1">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1">
         <v>298</v>
       </c>
-      <c r="K6" s="1">
-        <v>0</v>
-      </c>
-      <c r="L6" s="1">
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
         <v>197</v>
       </c>
-      <c r="M6" s="1">
+      <c r="O6" s="1">
         <v>197</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="P6" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1396,41 +1423,42 @@
       <c r="C7" s="2">
         <v>2877</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="2"/>
+      <c r="E7" s="1">
         <v>0.2</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>2467</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>8</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <v>2005</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <v>0.04</v>
       </c>
-      <c r="I7" s="1">
-        <v>1</v>
-      </c>
       <c r="J7" s="1">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1">
         <v>49</v>
       </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-      <c r="L7" s="1">
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
         <v>17</v>
       </c>
-      <c r="M7" s="1">
+      <c r="O7" s="1">
         <v>17</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="P7" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1440,41 +1468,41 @@
       <c r="C8" s="1">
         <v>375</v>
       </c>
-      <c r="D8" s="1">
+      <c r="E8" s="1">
         <v>0.23</v>
       </c>
-      <c r="E8" s="1">
+      <c r="F8" s="1">
         <v>314</v>
       </c>
-      <c r="F8" s="2">
-        <v>1</v>
-      </c>
-      <c r="G8" s="1">
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
         <v>2008</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>0.04</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
         <v>0.3</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="K8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K8" s="1">
-        <v>0</v>
-      </c>
-      <c r="L8" s="1">
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
         <v>0.4</v>
       </c>
-      <c r="M8" s="1">
+      <c r="O8" s="1">
         <v>0.4</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="P8" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -1484,43 +1512,44 @@
       <c r="C9" s="2">
         <v>10545</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="2"/>
+      <c r="E9" s="1">
         <v>0.13</v>
       </c>
-      <c r="E9" s="2">
+      <c r="F9" s="2">
         <v>9472</v>
       </c>
-      <c r="F9" s="2">
+      <c r="G9" s="2">
         <v>7</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>2001</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <v>0.04</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <v>0.5</v>
       </c>
-      <c r="J9" s="1">
+      <c r="K9" s="1">
         <v>95</v>
       </c>
-      <c r="K9" s="1">
+      <c r="M9" s="1">
         <v>0.2</v>
       </c>
-      <c r="L9" s="1">
+      <c r="N9" s="1">
         <v>41</v>
       </c>
-      <c r="M9" s="1">
+      <c r="O9" s="1">
         <v>42</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="P9" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>0</v>
@@ -1528,34 +1557,34 @@
       <c r="C10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="1">
+      <c r="F10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1">
         <v>0.04</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
         <v>0.5</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="1">
-        <v>0</v>
-      </c>
-      <c r="L10" s="1">
-        <v>0</v>
+      <c r="K10" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="M10" s="1">
         <v>0</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>0</v>
@@ -1563,41 +1592,42 @@
       <c r="C11" s="2">
         <v>83400</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="2"/>
+      <c r="E11" s="1">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2">
+      <c r="F11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2">
         <v>15</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
         <v>1993</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
         <v>0.04</v>
       </c>
-      <c r="I11" s="1">
-        <v>1</v>
-      </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" s="1">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="K11" s="1">
-        <v>30</v>
-      </c>
-      <c r="L11" s="1">
-        <v>0</v>
       </c>
       <c r="M11" s="1">
         <v>30</v>
       </c>
-      <c r="N11" s="1" t="s">
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1">
+        <v>30</v>
+      </c>
+      <c r="P11" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -1607,41 +1637,42 @@
       <c r="C12" s="2">
         <v>5700</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="2">
+      <c r="D12" s="2"/>
+      <c r="E12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
         <v>5700</v>
       </c>
-      <c r="F12" s="2">
+      <c r="G12" s="2">
         <v>5</v>
       </c>
-      <c r="G12" s="1">
+      <c r="H12" s="1">
         <v>2003</v>
       </c>
-      <c r="H12" s="1">
+      <c r="I12" s="1">
         <v>0.04</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12" s="1">
         <v>0.1</v>
       </c>
-      <c r="J12" s="1">
+      <c r="K12" s="1">
         <v>11.4</v>
-      </c>
-      <c r="K12" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="L12" s="1">
-        <v>0</v>
       </c>
       <c r="M12" s="1">
         <v>0.23</v>
       </c>
-      <c r="N12" s="1" t="s">
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="P12" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
@@ -1651,41 +1682,42 @@
       <c r="C13" s="2">
         <v>18813</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="2"/>
+      <c r="E13" s="1">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="E13" s="2">
+      <c r="F13" s="2">
         <v>17752</v>
       </c>
-      <c r="F13" s="2">
+      <c r="G13" s="2">
         <v>6</v>
       </c>
-      <c r="G13" s="1">
+      <c r="H13" s="1">
         <v>2002</v>
       </c>
-      <c r="H13" s="1">
+      <c r="I13" s="1">
         <v>4.7E-2</v>
       </c>
-      <c r="I13" s="1">
-        <v>1</v>
-      </c>
       <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
         <v>417</v>
       </c>
-      <c r="K13" s="1">
+      <c r="M13" s="1">
         <v>6.7</v>
       </c>
-      <c r="L13" s="1">
+      <c r="N13" s="1">
         <v>122</v>
       </c>
-      <c r="M13" s="1">
+      <c r="O13" s="1">
         <v>130</v>
       </c>
-      <c r="N13" s="1" t="s">
+      <c r="P13" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
@@ -1695,44 +1727,45 @@
       <c r="C14" s="2">
         <v>11146</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="2"/>
+      <c r="E14" s="1">
         <v>0.24199999999999999</v>
       </c>
-      <c r="E14" s="2">
+      <c r="F14" s="2">
         <v>9116</v>
       </c>
-      <c r="F14" s="2">
+      <c r="G14" s="2">
         <v>11</v>
       </c>
-      <c r="G14" s="1">
+      <c r="H14" s="1">
         <v>1997</v>
       </c>
-      <c r="H14" s="1">
+      <c r="I14" s="1">
         <v>0.04</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14" s="1">
         <v>0.5</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="K14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="1">
-        <v>0</v>
-      </c>
-      <c r="M14" s="1">
-        <v>0</v>
-      </c>
-      <c r="N14" s="1" t="s">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1">
+        <v>0</v>
+      </c>
+      <c r="P14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O14" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q14" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
@@ -1742,41 +1775,42 @@
       <c r="C15" s="2">
         <v>31046</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="2"/>
+      <c r="E15" s="1">
         <v>0.214</v>
       </c>
-      <c r="E15" s="2">
+      <c r="F15" s="2">
         <v>25987</v>
       </c>
-      <c r="F15" s="2">
+      <c r="G15" s="2">
         <v>10</v>
       </c>
-      <c r="G15" s="1">
+      <c r="H15" s="1">
         <v>1998</v>
       </c>
-      <c r="H15" s="1">
+      <c r="I15" s="1">
         <v>0.04</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15" s="1">
         <v>0.5</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="K15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K15" s="1">
+      <c r="M15" s="1">
         <v>71</v>
       </c>
-      <c r="L15" s="1">
-        <v>0</v>
-      </c>
-      <c r="M15" s="1">
+      <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
         <v>73</v>
       </c>
-      <c r="N15" s="1" t="s">
+      <c r="P15" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
@@ -1786,41 +1820,42 @@
       <c r="C16" s="2">
         <v>48215</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="2"/>
+      <c r="E16" s="1">
         <v>0.223</v>
       </c>
-      <c r="E16" s="2">
+      <c r="F16" s="2">
         <v>40039</v>
       </c>
-      <c r="F16" s="2">
+      <c r="G16" s="2">
         <v>9</v>
       </c>
-      <c r="G16" s="1">
+      <c r="H16" s="1">
         <v>1999</v>
       </c>
-      <c r="H16" s="1">
+      <c r="I16" s="1">
         <v>0.04</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16" s="1">
         <v>0.5</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="K16" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="1">
-        <v>0</v>
-      </c>
-      <c r="L16" s="1">
-        <v>0</v>
-      </c>
       <c r="M16" s="1">
         <v>0</v>
       </c>
-      <c r="N16" s="1" t="s">
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
@@ -1830,44 +1865,46 @@
       <c r="C17" s="2">
         <v>112391</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="2"/>
+      <c r="E17" s="1">
         <v>0.04</v>
       </c>
-      <c r="E17" s="2">
+      <c r="F17" s="2">
         <v>108670</v>
       </c>
-      <c r="F17" s="2">
+      <c r="G17" s="2">
         <v>10</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H17" s="1">
+      <c r="H17" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I17" s="1">
         <v>0.12</v>
       </c>
-      <c r="I17" s="1">
+      <c r="J17" s="1">
         <v>0.5</v>
       </c>
-      <c r="J17" s="2">
+      <c r="K17" s="2">
         <v>3260</v>
       </c>
-      <c r="K17" s="1">
-        <v>0</v>
-      </c>
-      <c r="L17" s="1">
+      <c r="L17" s="2"/>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1">
         <v>782</v>
       </c>
-      <c r="M17" s="1">
+      <c r="O17" s="1">
         <v>783</v>
       </c>
-      <c r="N17" s="1" t="s">
+      <c r="P17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="O17" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q17" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
@@ -1877,44 +1914,46 @@
       <c r="C18" s="2">
         <v>45975</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="2"/>
+      <c r="E18" s="1">
         <v>0.04</v>
       </c>
-      <c r="E18" s="2">
+      <c r="F18" s="2">
         <v>44453</v>
       </c>
-      <c r="F18" s="2">
+      <c r="G18" s="2">
         <v>9</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="H18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1334</v>
+      </c>
+      <c r="L18" s="2"/>
+      <c r="M18" s="1">
+        <v>24</v>
+      </c>
+      <c r="N18" s="1">
+        <v>807</v>
+      </c>
+      <c r="O18" s="1">
+        <v>832</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H18" s="1">
-        <v>0.12</v>
-      </c>
-      <c r="I18" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="J18" s="2">
-        <v>1334</v>
-      </c>
-      <c r="K18" s="1">
-        <v>24</v>
-      </c>
-      <c r="L18" s="1">
-        <v>807</v>
-      </c>
-      <c r="M18" s="1">
-        <v>832</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="O18" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
@@ -1924,44 +1963,45 @@
       <c r="C19" s="2">
         <v>21651</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="2"/>
+      <c r="E19" s="1">
         <v>0.1</v>
       </c>
-      <c r="E19" s="2">
+      <c r="F19" s="2">
         <v>20109</v>
       </c>
-      <c r="F19" s="2">
+      <c r="G19" s="2">
         <v>8</v>
       </c>
-      <c r="G19" s="1">
+      <c r="H19" s="1">
         <v>2000</v>
       </c>
-      <c r="H19" s="1">
+      <c r="I19" s="1">
         <v>0.12</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J19" s="1">
         <v>0.5</v>
       </c>
-      <c r="J19" s="1">
+      <c r="K19" s="1">
         <v>603</v>
       </c>
-      <c r="K19" s="1">
+      <c r="M19" s="1">
         <v>2.9</v>
       </c>
-      <c r="L19" s="1">
+      <c r="N19" s="1">
         <v>96</v>
       </c>
-      <c r="M19" s="1">
+      <c r="O19" s="1">
         <v>100</v>
       </c>
-      <c r="N19" s="1" t="s">
+      <c r="P19" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="O19" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q19" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -1971,343 +2011,349 @@
       <c r="C20" s="1">
         <v>938</v>
       </c>
-      <c r="D20" s="1">
+      <c r="E20" s="1">
         <v>0.3</v>
       </c>
-      <c r="E20" s="1">
+      <c r="F20" s="1">
         <v>732</v>
       </c>
-      <c r="F20" s="2">
-        <v>1</v>
-      </c>
-      <c r="G20" s="1">
+      <c r="G20" s="2">
+        <v>1</v>
+      </c>
+      <c r="H20" s="1">
         <v>2006</v>
       </c>
-      <c r="H20" s="1">
+      <c r="I20" s="1">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I20" s="1">
+      <c r="J20" s="1">
         <v>0.1</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="K20" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="L20" s="1">
+        <v>2</v>
+      </c>
+      <c r="M20" s="1">
         <v>0.2</v>
       </c>
-      <c r="L20" s="1">
+      <c r="N20" s="1">
         <v>0.2</v>
       </c>
-      <c r="M20" s="1">
+      <c r="O20" s="1">
         <v>0.4</v>
       </c>
-      <c r="N20" s="1" t="s">
+      <c r="P20" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C21" s="2">
         <v>7469</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="2"/>
+      <c r="E21" s="1">
         <v>0.3</v>
       </c>
-      <c r="E21" s="2">
+      <c r="F21" s="2">
         <v>5833</v>
       </c>
-      <c r="F21" s="2">
+      <c r="G21" s="2">
         <v>3</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H21" s="1">
+      <c r="H21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I21" s="1">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I21" s="1">
+      <c r="J21" s="1">
         <v>0.1</v>
       </c>
-      <c r="J21" s="1">
+      <c r="K21" s="1">
         <v>20.399999999999999</v>
       </c>
-      <c r="K21" s="1">
+      <c r="M21" s="1">
         <v>3.6</v>
       </c>
-      <c r="L21" s="1">
-        <v>0</v>
-      </c>
-      <c r="M21" s="1">
+      <c r="N21" s="1">
+        <v>0</v>
+      </c>
+      <c r="O21" s="1">
         <v>5.4</v>
       </c>
-      <c r="N21" s="1" t="s">
+      <c r="P21" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C22" s="2">
         <v>2883</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="2"/>
+      <c r="E22" s="1">
         <v>0.12</v>
       </c>
-      <c r="E22" s="2">
+      <c r="F22" s="2">
         <v>2251</v>
       </c>
-      <c r="F22" s="2"/>
-      <c r="H22" s="1">
+      <c r="G22" s="2"/>
+      <c r="I22" s="1">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I22" s="1">
+      <c r="J22" s="1">
         <v>0.1</v>
       </c>
-      <c r="J22" s="1">
+      <c r="K22" s="1">
         <v>7.8</v>
       </c>
-      <c r="K22" s="1">
+      <c r="M22" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="L22" s="1">
-        <v>0</v>
-      </c>
-      <c r="M22" s="1">
+      <c r="N22" s="1">
+        <v>0</v>
+      </c>
+      <c r="O22" s="1">
         <v>3.8</v>
       </c>
-      <c r="N22" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="C23" s="2">
         <v>1123</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E23" s="2">
+      <c r="D23" s="2"/>
+      <c r="E23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
         <v>1123</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G23" s="1">
+      <c r="G23" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H23" s="1">
         <v>2003</v>
       </c>
-      <c r="H23" s="1">
+      <c r="I23" s="1">
         <v>0.04</v>
       </c>
-      <c r="I23" s="1">
+      <c r="J23" s="1">
         <v>0.5</v>
       </c>
-      <c r="J23" s="1">
+      <c r="K23" s="1">
         <v>11.2</v>
-      </c>
-      <c r="K23" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L23" s="1">
-        <v>0</v>
       </c>
       <c r="M23" s="1">
         <v>1.5</v>
       </c>
-      <c r="N23" s="1" t="s">
+      <c r="N23" s="1">
+        <v>0</v>
+      </c>
+      <c r="O23" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="P23" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="O23" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q23" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C24" s="1">
         <v>216</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E24" s="1">
+      <c r="E24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1">
         <v>216</v>
       </c>
-      <c r="H24" s="1">
+      <c r="I24" s="1">
         <v>0.04</v>
       </c>
-      <c r="I24" s="1">
+      <c r="J24" s="1">
         <v>0.5</v>
       </c>
-      <c r="J24" s="1">
+      <c r="K24" s="1">
         <v>2.16</v>
       </c>
-      <c r="K24" s="1">
-        <v>0</v>
-      </c>
-      <c r="L24" s="1">
-        <v>0</v>
-      </c>
       <c r="M24" s="1">
         <v>0</v>
       </c>
-      <c r="N24" s="1" t="s">
+      <c r="N24" s="1">
+        <v>0</v>
+      </c>
+      <c r="O24" s="1">
+        <v>0</v>
+      </c>
+      <c r="P24" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="O24" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q24" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C25" s="1">
         <v>7</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E25" s="1">
+      <c r="E25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1">
         <v>7</v>
       </c>
-      <c r="H25" s="1">
+      <c r="I25" s="1">
         <v>0.04</v>
       </c>
-      <c r="I25" s="1">
+      <c r="J25" s="1">
         <v>0.1</v>
       </c>
-      <c r="J25" s="1">
-        <v>0</v>
-      </c>
       <c r="K25" s="1">
         <v>0</v>
       </c>
-      <c r="L25" s="1">
-        <v>0</v>
-      </c>
       <c r="M25" s="1">
         <v>0</v>
       </c>
-      <c r="N25" s="1" t="s">
+      <c r="N25" s="1">
+        <v>0</v>
+      </c>
+      <c r="O25" s="1">
+        <v>0</v>
+      </c>
+      <c r="P25" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O25" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q25" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C26" s="1">
         <v>314</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E26" s="1">
+      <c r="E26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1">
         <v>314</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G26" s="1">
+      <c r="G26" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H26" s="1">
         <v>2003</v>
       </c>
-      <c r="H26" s="1">
+      <c r="I26" s="1">
         <v>0.04</v>
       </c>
-      <c r="I26" s="1">
+      <c r="J26" s="1">
         <v>0.5</v>
       </c>
-      <c r="J26" s="1">
+      <c r="K26" s="1">
         <v>3.1</v>
-      </c>
-      <c r="K26" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="L26" s="1">
-        <v>0</v>
       </c>
       <c r="M26" s="1">
         <v>0.4</v>
       </c>
-      <c r="N26" s="1" t="s">
+      <c r="N26" s="1">
+        <v>0</v>
+      </c>
+      <c r="O26" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="P26" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="O26" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q26" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27" s="1">
         <v>314</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E27" s="1">
+      <c r="E27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1">
         <v>314</v>
       </c>
-      <c r="H27" s="1">
+      <c r="I27" s="1">
         <v>0.04</v>
       </c>
-      <c r="I27" s="1">
+      <c r="J27" s="1">
         <v>0.5</v>
       </c>
-      <c r="J27" s="1">
+      <c r="K27" s="1">
         <v>3.1</v>
       </c>
-      <c r="K27" s="1">
-        <v>0</v>
-      </c>
-      <c r="L27" s="1">
-        <v>0</v>
-      </c>
       <c r="M27" s="1">
         <v>0</v>
       </c>
-      <c r="N27" s="1" t="s">
+      <c r="N27" s="1">
+        <v>0</v>
+      </c>
+      <c r="O27" s="1">
+        <v>0</v>
+      </c>
+      <c r="P27" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="O27" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q27" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>0</v>
@@ -2315,34 +2361,34 @@
       <c r="C28" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H28" s="1">
+      <c r="F28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I28" s="1">
         <v>0.04</v>
       </c>
-      <c r="I28" s="1">
+      <c r="J28" s="1">
         <v>0.5</v>
       </c>
-      <c r="J28" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K28" s="1">
-        <v>0.32</v>
-      </c>
-      <c r="L28" s="1">
-        <v>0</v>
+      <c r="K28" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="M28" s="1">
         <v>0.32</v>
       </c>
-      <c r="N28" s="1" t="s">
+      <c r="N28" s="1">
+        <v>0</v>
+      </c>
+      <c r="O28" s="1">
+        <v>0.32</v>
+      </c>
+      <c r="P28" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>17</v>
@@ -2350,9 +2396,6 @@
       <c r="C29" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="E29" s="1" t="s">
         <v>1</v>
       </c>
@@ -2362,376 +2405,391 @@
       <c r="G29" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H29" s="1">
+      <c r="H29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I29" s="1">
         <v>0.04</v>
       </c>
-      <c r="I29" s="1">
+      <c r="J29" s="1">
         <v>0.1</v>
       </c>
-      <c r="J29" s="1">
-        <v>0</v>
-      </c>
       <c r="K29" s="1">
         <v>0</v>
       </c>
-      <c r="L29" s="1">
-        <v>0</v>
-      </c>
       <c r="M29" s="1">
         <v>0</v>
       </c>
-      <c r="N29" s="1" t="s">
+      <c r="N29" s="1">
+        <v>0</v>
+      </c>
+      <c r="O29" s="1">
+        <v>0</v>
+      </c>
+      <c r="P29" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="C30" s="2">
         <v>687902</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E30" s="2">
+      <c r="D30" s="2"/>
+      <c r="E30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
         <v>676416</v>
       </c>
-      <c r="F30" s="2">
-        <v>1</v>
-      </c>
-      <c r="G30" s="1">
+      <c r="G30" s="2">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1">
         <v>2007</v>
       </c>
-      <c r="H30" s="1">
+      <c r="I30" s="1">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="I30" s="1">
+      <c r="J30" s="1">
         <v>0.5</v>
       </c>
-      <c r="J30" s="2">
+      <c r="K30" s="2">
         <v>14543</v>
       </c>
-      <c r="K30" s="1">
+      <c r="L30" s="2"/>
+      <c r="M30" s="1">
         <v>1.9</v>
       </c>
-      <c r="L30" s="1">
+      <c r="N30" s="1">
         <v>593</v>
       </c>
-      <c r="M30" s="1">
+      <c r="O30" s="1">
         <v>596</v>
       </c>
-      <c r="N30" s="1" t="s">
+      <c r="P30" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C31" s="2">
         <v>26880</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="D31" s="2"/>
       <c r="E31" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G31" s="1">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H31" s="1">
         <v>1990</v>
       </c>
-      <c r="H31" s="1">
+      <c r="I31" s="1">
         <v>0.04</v>
       </c>
-      <c r="I31" s="1">
+      <c r="J31" s="1">
         <v>0.5</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="K31" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K31" s="1">
-        <v>0</v>
-      </c>
-      <c r="L31" s="1">
-        <v>0</v>
-      </c>
       <c r="M31" s="1">
         <v>0</v>
       </c>
-      <c r="N31" s="1" t="s">
+      <c r="N31" s="1">
+        <v>0</v>
+      </c>
+      <c r="O31" s="1">
+        <v>0</v>
+      </c>
+      <c r="P31" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" s="2">
+        <v>49000</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1">
+        <v>2008</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="J32" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M32" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="N32" s="1">
+        <v>193</v>
+      </c>
+      <c r="O32" s="1">
+        <v>194</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C32" s="1" t="s">
+      <c r="B33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="J33" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M33" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="N33" s="2">
+        <v>9567</v>
+      </c>
+      <c r="O33" s="2">
+        <v>9568</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F32" s="1">
-        <v>1</v>
-      </c>
-      <c r="G32" s="1">
-        <v>2008</v>
-      </c>
-      <c r="H32" s="1">
-        <v>0.12</v>
-      </c>
-      <c r="I32" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K32" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="L32" s="1">
-        <v>193</v>
-      </c>
-      <c r="M32" s="1">
-        <v>194</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H33" s="1">
-        <v>0.12</v>
-      </c>
-      <c r="I33" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K33" s="1">
-        <v>0.46</v>
-      </c>
-      <c r="L33" s="2">
-        <v>9567</v>
-      </c>
-      <c r="M33" s="2">
-        <v>9568</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="C34" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H34" s="1">
+      <c r="F34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I34" s="1">
         <v>0.04</v>
       </c>
-      <c r="I34" s="1">
+      <c r="J34" s="1">
         <v>0.1</v>
       </c>
-      <c r="J34" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K34" s="1">
-        <v>2</v>
-      </c>
-      <c r="L34" s="1">
-        <v>0</v>
+      <c r="K34" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="M34" s="1">
         <v>2</v>
       </c>
-      <c r="N34" s="1" t="s">
+      <c r="N34" s="1">
+        <v>0</v>
+      </c>
+      <c r="O34" s="1">
+        <v>2</v>
+      </c>
+      <c r="P34" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="J35" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M35" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="N35" s="2">
+        <v>5265</v>
+      </c>
+      <c r="O35" s="2">
+        <v>5266</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I36" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="J36" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M36" s="1">
+        <v>0</v>
+      </c>
+      <c r="N36" s="1">
+        <v>0</v>
+      </c>
+      <c r="O36" s="1">
+        <v>0</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H35" s="1">
+      <c r="C37" s="1">
+        <f>AVERAGE(45095, 55832)</f>
+        <v>50463.5</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F37" s="2">
+        <v>44404</v>
+      </c>
+      <c r="G37" s="2">
+        <v>3</v>
+      </c>
+      <c r="H37" s="1">
+        <v>2005</v>
+      </c>
+      <c r="I37" s="1">
         <v>0.12</v>
       </c>
-      <c r="I35" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K35" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="L35" s="2">
-        <v>5265</v>
-      </c>
-      <c r="M35" s="2">
-        <v>5266</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H36" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="I36" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K36" s="1">
-        <v>0</v>
-      </c>
-      <c r="L36" s="1">
-        <v>0</v>
-      </c>
-      <c r="M36" s="1">
-        <v>0</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
+      <c r="J37" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="K37" s="2">
+        <v>1998</v>
+      </c>
+      <c r="L37" s="2"/>
+      <c r="M37" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="N37" s="1">
+        <v>11</v>
+      </c>
+      <c r="O37" s="1">
+        <v>15.6</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E37" s="2">
-        <v>44404</v>
-      </c>
-      <c r="F37" s="2">
-        <v>3</v>
-      </c>
-      <c r="G37" s="1">
-        <v>2005</v>
-      </c>
-      <c r="H37" s="1">
-        <v>0.12</v>
-      </c>
-      <c r="I37" s="1">
-        <v>0.75</v>
-      </c>
-      <c r="J37" s="2">
-        <v>1998</v>
-      </c>
-      <c r="K37" s="1">
-        <v>1.4</v>
-      </c>
-      <c r="L37" s="1">
-        <v>11</v>
-      </c>
-      <c r="M37" s="1">
-        <v>15.6</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="C38" s="2">
         <v>41197</v>
       </c>
-      <c r="E38" s="2">
+      <c r="D38" s="2"/>
+      <c r="F38" s="2">
         <v>41197</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>3</v>
       </c>
-      <c r="G38" s="1">
+      <c r="H38" s="1">
         <v>2008</v>
       </c>
-      <c r="H38" s="1">
+      <c r="I38" s="1">
         <v>0.12</v>
       </c>
-      <c r="I38" s="1">
+      <c r="J38" s="1">
         <v>0.1</v>
       </c>
-      <c r="J38" s="1">
+      <c r="K38" s="1">
         <v>247</v>
       </c>
-      <c r="K38" s="1">
+      <c r="M38" s="1">
         <v>26.2</v>
       </c>
-      <c r="L38" s="1">
+      <c r="N38" s="1">
         <v>206</v>
       </c>
-      <c r="M38" s="1">
+      <c r="O38" s="1">
         <v>233</v>
       </c>
-      <c r="N38" s="1" t="s">
+      <c r="P38" s="1" t="s">
         <v>11</v>
       </c>
     </row>

--- a/data/sars/alaska/tables/Alaska_2009_Appendix2.xlsx
+++ b/data/sars/alaska/tables/Alaska_2009_Appendix2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/alaska/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53CBB976-CA56-D14F-AAFF-EFC855EC460F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203FF8D5-FE46-FB4F-8FD2-FFCECD303B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="16980" windowHeight="19820" xr2:uid="{96A13700-2429-4246-A404-86EBBE95C8D2}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="28220" windowHeight="20740" xr2:uid="{96A13700-2429-4246-A404-86EBBE95C8D2}"/>
   </bookViews>
   <sheets>
     <sheet name="tabula-Alaska_2009_Appendix2" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="80">
   <si>
     <t>Alaska</t>
   </si>
@@ -267,6 +267,12 @@
   </si>
   <si>
     <t>pbr_notes</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -415,7 +421,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -593,6 +599,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -756,7 +768,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -764,10 +776,19 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1145,7 +1166,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18281ADD-1771-3845-B0AA-B7D49286D42F}">
-  <dimension ref="A1:Q38"/>
+  <dimension ref="A1:R38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.1640625" style="1" customWidth="1"/>
@@ -1155,7 +1176,7 @@
     <col min="5" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>59</v>
       </c>
@@ -1205,10 +1226,13 @@
         <v>72</v>
       </c>
       <c r="Q1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>43</v>
       </c>
@@ -1243,42 +1267,45 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="1">
+      <c r="B3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="4">
         <v>0.12</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="4">
         <v>0.5</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" s="1">
-        <v>1</v>
-      </c>
-      <c r="N3" s="2">
+      <c r="K3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" s="4">
+        <v>1</v>
+      </c>
+      <c r="N3" s="5">
         <v>6788</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3" s="5">
         <v>6789</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="P3" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q3" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1323,7 +1350,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1368,7 +1395,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1413,7 +1440,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1458,96 +1485,102 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="4">
         <v>375</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="4">
         <v>0.23</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="4">
         <v>314</v>
       </c>
-      <c r="G8" s="2">
-        <v>1</v>
-      </c>
-      <c r="H8" s="1">
+      <c r="G8" s="5">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4">
         <v>2008</v>
       </c>
-      <c r="I8" s="1">
+      <c r="I8" s="4">
         <v>0.04</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="4">
         <v>0.3</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="K8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M8" s="1">
-        <v>0</v>
-      </c>
-      <c r="N8" s="1">
+      <c r="M8" s="4">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4">
         <v>0.4</v>
       </c>
-      <c r="O8" s="1">
+      <c r="O8" s="4">
         <v>0.4</v>
       </c>
-      <c r="P8" s="1" t="s">
+      <c r="P8" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="Q8" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="5">
         <v>10545</v>
       </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="1">
+      <c r="D9" s="5"/>
+      <c r="E9" s="4">
         <v>0.13</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="5">
         <v>9472</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="5">
         <v>7</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9" s="4">
         <v>2001</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="4">
         <v>0.04</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="4">
         <v>0.5</v>
       </c>
-      <c r="K9" s="1">
+      <c r="K9" s="4">
         <v>95</v>
       </c>
-      <c r="M9" s="1">
+      <c r="M9" s="4">
         <v>0.2</v>
       </c>
-      <c r="N9" s="1">
+      <c r="N9" s="4">
         <v>41</v>
       </c>
-      <c r="O9" s="1">
+      <c r="O9" s="4">
         <v>42</v>
       </c>
-      <c r="P9" s="1" t="s">
+      <c r="P9" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>44</v>
       </c>
@@ -1582,97 +1615,103 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="2">
+      <c r="B11" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5">
         <v>83400</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="1">
+      <c r="D11" s="5"/>
+      <c r="E11" s="4">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2">
+      <c r="F11" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5">
         <v>15</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11" s="4">
         <v>1993</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I11" s="4">
         <v>0.04</v>
       </c>
-      <c r="J11" s="1">
-        <v>1</v>
-      </c>
-      <c r="K11" s="1" t="s">
+      <c r="J11" s="4">
+        <v>1</v>
+      </c>
+      <c r="K11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M11" s="1">
+      <c r="M11" s="4">
         <v>30</v>
       </c>
-      <c r="N11" s="1">
-        <v>0</v>
-      </c>
-      <c r="O11" s="1">
+      <c r="N11" s="4">
+        <v>0</v>
+      </c>
+      <c r="O11" s="4">
         <v>30</v>
       </c>
-      <c r="P11" s="1" t="s">
+      <c r="P11" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
+      <c r="Q11" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="5">
         <v>5700</v>
       </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="2">
+      <c r="D12" s="5"/>
+      <c r="E12" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5">
         <v>5700</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="5">
         <v>5</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12" s="4">
         <v>2003</v>
       </c>
-      <c r="I12" s="1">
+      <c r="I12" s="4">
         <v>0.04</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12" s="4">
         <v>0.1</v>
       </c>
-      <c r="K12" s="1">
+      <c r="K12" s="4">
         <v>11.4</v>
       </c>
-      <c r="M12" s="1">
+      <c r="M12" s="4">
         <v>0.23</v>
       </c>
-      <c r="N12" s="1">
-        <v>0</v>
-      </c>
-      <c r="O12" s="1">
+      <c r="N12" s="4">
+        <v>0</v>
+      </c>
+      <c r="O12" s="4">
         <v>0.23</v>
       </c>
-      <c r="P12" s="1" t="s">
+      <c r="P12" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
@@ -1717,423 +1756,450 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="5">
         <v>11146</v>
       </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="1">
+      <c r="D14" s="5"/>
+      <c r="E14" s="4">
         <v>0.24199999999999999</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="5">
         <v>9116</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="5">
         <v>11</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H14" s="4">
         <v>1997</v>
       </c>
-      <c r="I14" s="1">
+      <c r="I14" s="4">
         <v>0.04</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14" s="4">
         <v>0.5</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="K14" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="1">
-        <v>0</v>
-      </c>
-      <c r="O14" s="1">
-        <v>0</v>
-      </c>
-      <c r="P14" s="1" t="s">
+      <c r="M14" s="6">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4">
+        <v>0</v>
+      </c>
+      <c r="P14" s="4" t="s">
         <v>11</v>
       </c>
       <c r="Q14" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="R14" s="7" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="5">
         <v>31046</v>
       </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="1">
+      <c r="D15" s="5"/>
+      <c r="E15" s="4">
         <v>0.214</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="5">
         <v>25987</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="5">
         <v>10</v>
       </c>
-      <c r="H15" s="1">
+      <c r="H15" s="4">
         <v>1998</v>
       </c>
-      <c r="I15" s="1">
+      <c r="I15" s="4">
         <v>0.04</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J15" s="4">
         <v>0.5</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="K15" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M15" s="1">
+      <c r="M15" s="4">
         <v>71</v>
       </c>
-      <c r="N15" s="1">
-        <v>0</v>
-      </c>
-      <c r="O15" s="1">
+      <c r="N15" s="4">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4">
         <v>73</v>
       </c>
-      <c r="P15" s="1" t="s">
+      <c r="P15" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
+      <c r="Q15" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="5">
         <v>48215</v>
       </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="1">
+      <c r="D16" s="5"/>
+      <c r="E16" s="4">
         <v>0.223</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="5">
         <v>40039</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="5">
         <v>9</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H16" s="4">
         <v>1999</v>
       </c>
-      <c r="I16" s="1">
+      <c r="I16" s="4">
         <v>0.04</v>
       </c>
-      <c r="J16" s="1">
+      <c r="J16" s="4">
         <v>0.5</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="K16" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M16" s="1">
-        <v>0</v>
-      </c>
-      <c r="N16" s="1">
-        <v>0</v>
-      </c>
-      <c r="O16" s="1">
-        <v>0</v>
-      </c>
-      <c r="P16" s="1" t="s">
+      <c r="M16" s="4">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4">
+        <v>0</v>
+      </c>
+      <c r="P16" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
+      <c r="Q16" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="5">
         <v>112391</v>
       </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="1">
+      <c r="D17" s="5"/>
+      <c r="E17" s="4">
         <v>0.04</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="5">
         <v>108670</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="5">
         <v>10</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="I17" s="1">
+      <c r="I17" s="4">
         <v>0.12</v>
       </c>
-      <c r="J17" s="1">
+      <c r="J17" s="4">
         <v>0.5</v>
       </c>
-      <c r="K17" s="2">
+      <c r="K17" s="5">
         <v>3260</v>
       </c>
-      <c r="L17" s="2"/>
-      <c r="M17" s="1">
-        <v>0</v>
-      </c>
-      <c r="N17" s="1">
+      <c r="L17" s="5"/>
+      <c r="M17" s="4">
+        <v>0</v>
+      </c>
+      <c r="N17" s="4">
         <v>782</v>
       </c>
-      <c r="O17" s="1">
+      <c r="O17" s="4">
         <v>783</v>
       </c>
-      <c r="P17" s="1" t="s">
+      <c r="P17" s="4" t="s">
         <v>2</v>
       </c>
       <c r="Q17" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="R17" s="7" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="5">
         <v>45975</v>
       </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="1">
+      <c r="D18" s="5"/>
+      <c r="E18" s="4">
         <v>0.04</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="5">
         <v>44453</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" s="5">
         <v>9</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="I18" s="1">
+      <c r="I18" s="4">
         <v>0.12</v>
       </c>
-      <c r="J18" s="1">
+      <c r="J18" s="4">
         <v>0.5</v>
       </c>
-      <c r="K18" s="2">
+      <c r="K18" s="5">
         <v>1334</v>
       </c>
-      <c r="L18" s="2"/>
-      <c r="M18" s="1">
+      <c r="L18" s="5"/>
+      <c r="M18" s="4">
         <v>24</v>
       </c>
-      <c r="N18" s="1">
+      <c r="N18" s="4">
         <v>807</v>
       </c>
-      <c r="O18" s="1">
+      <c r="O18" s="4">
         <v>832</v>
       </c>
-      <c r="P18" s="1" t="s">
+      <c r="P18" s="4" t="s">
         <v>2</v>
       </c>
       <c r="Q18" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="R18" s="7" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="5">
         <v>21651</v>
       </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="1">
+      <c r="D19" s="5"/>
+      <c r="E19" s="4">
         <v>0.1</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="5">
         <v>20109</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" s="5">
         <v>8</v>
       </c>
-      <c r="H19" s="1">
+      <c r="H19" s="4">
         <v>2000</v>
       </c>
-      <c r="I19" s="1">
+      <c r="I19" s="4">
         <v>0.12</v>
       </c>
-      <c r="J19" s="1">
+      <c r="J19" s="4">
         <v>0.5</v>
       </c>
-      <c r="K19" s="1">
+      <c r="K19" s="4">
         <v>603</v>
       </c>
-      <c r="M19" s="1">
+      <c r="M19" s="4">
         <v>2.9</v>
       </c>
-      <c r="N19" s="1">
+      <c r="N19" s="4">
         <v>96</v>
       </c>
-      <c r="O19" s="1">
+      <c r="O19" s="4">
         <v>100</v>
       </c>
-      <c r="P19" s="1" t="s">
+      <c r="P19" s="4" t="s">
         <v>2</v>
       </c>
       <c r="Q19" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="R19" s="7" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="4">
         <v>938</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="4">
         <v>0.3</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="4">
         <v>732</v>
       </c>
-      <c r="G20" s="2">
-        <v>1</v>
-      </c>
-      <c r="H20" s="1">
+      <c r="G20" s="5">
+        <v>1</v>
+      </c>
+      <c r="H20" s="4">
         <v>2006</v>
       </c>
-      <c r="I20" s="1">
+      <c r="I20" s="4">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J20" s="4">
         <v>0.1</v>
       </c>
-      <c r="K20" s="1">
+      <c r="K20" s="4">
         <v>2.6</v>
       </c>
-      <c r="L20" s="1">
+      <c r="L20" s="4">
         <v>2</v>
       </c>
-      <c r="M20" s="1">
+      <c r="M20" s="4">
         <v>0.2</v>
       </c>
-      <c r="N20" s="1">
+      <c r="N20" s="4">
         <v>0.2</v>
       </c>
-      <c r="O20" s="1">
+      <c r="O20" s="4">
         <v>0.4</v>
       </c>
-      <c r="P20" s="1" t="s">
+      <c r="P20" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
+      <c r="Q20" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="5">
         <v>7469</v>
       </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="1">
+      <c r="D21" s="5"/>
+      <c r="E21" s="4">
         <v>0.3</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="5">
         <v>5833</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21" s="5">
         <v>3</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="I21" s="1">
+      <c r="I21" s="4">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="4">
         <v>0.1</v>
       </c>
-      <c r="K21" s="1">
+      <c r="K21" s="4">
         <v>20.399999999999999</v>
       </c>
-      <c r="M21" s="1">
+      <c r="M21" s="4">
         <v>3.6</v>
       </c>
-      <c r="N21" s="1">
-        <v>0</v>
-      </c>
-      <c r="O21" s="1">
+      <c r="N21" s="4">
+        <v>0</v>
+      </c>
+      <c r="O21" s="4">
         <v>5.4</v>
       </c>
-      <c r="P21" s="1" t="s">
+      <c r="P21" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
+      <c r="Q21" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="5">
         <v>2883</v>
       </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="1">
+      <c r="D22" s="5"/>
+      <c r="E22" s="4">
         <v>0.12</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="5">
         <v>2251</v>
       </c>
-      <c r="G22" s="2"/>
-      <c r="I22" s="1">
+      <c r="G22" s="5"/>
+      <c r="I22" s="4">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22" s="4">
         <v>0.1</v>
       </c>
-      <c r="K22" s="1">
+      <c r="K22" s="4">
         <v>7.8</v>
       </c>
-      <c r="M22" s="1">
+      <c r="M22" s="4">
         <v>2.2000000000000002</v>
       </c>
-      <c r="N22" s="1">
-        <v>0</v>
-      </c>
-      <c r="O22" s="1">
+      <c r="N22" s="4">
+        <v>0</v>
+      </c>
+      <c r="O22" s="4">
         <v>3.8</v>
       </c>
-      <c r="P22" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="P22" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>26</v>
       </c>
@@ -2177,11 +2243,11 @@
       <c r="P23" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q23" s="4" t="s">
+      <c r="R23" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>26</v>
       </c>
@@ -2218,52 +2284,55 @@
       <c r="P24" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q24" s="4" t="s">
+      <c r="R24" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
+    <row r="25" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="4">
         <v>7</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F25" s="1">
+      <c r="E25" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="4">
         <v>7</v>
       </c>
-      <c r="I25" s="1">
+      <c r="I25" s="4">
         <v>0.04</v>
       </c>
-      <c r="J25" s="1">
+      <c r="J25" s="4">
         <v>0.1</v>
       </c>
-      <c r="K25" s="1">
-        <v>0</v>
-      </c>
-      <c r="M25" s="1">
-        <v>0</v>
-      </c>
-      <c r="N25" s="1">
-        <v>0</v>
-      </c>
-      <c r="O25" s="1">
-        <v>0</v>
-      </c>
-      <c r="P25" s="1" t="s">
+      <c r="K25" s="4">
+        <v>0</v>
+      </c>
+      <c r="M25" s="4">
+        <v>0</v>
+      </c>
+      <c r="N25" s="4">
+        <v>0</v>
+      </c>
+      <c r="O25" s="4">
+        <v>0</v>
+      </c>
+      <c r="P25" s="4" t="s">
         <v>11</v>
       </c>
       <c r="Q25" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="R25" s="7" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>26</v>
       </c>
@@ -2306,11 +2375,11 @@
       <c r="P26" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q26" s="4" t="s">
+      <c r="R26" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
@@ -2347,11 +2416,11 @@
       <c r="P27" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q27" s="4" t="s">
+      <c r="R27" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>30</v>
       </c>
@@ -2386,291 +2455,312 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I29" s="1">
+      <c r="C29" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I29" s="4">
         <v>0.04</v>
       </c>
-      <c r="J29" s="1">
+      <c r="J29" s="4">
         <v>0.1</v>
       </c>
-      <c r="K29" s="1">
-        <v>0</v>
-      </c>
-      <c r="M29" s="1">
-        <v>0</v>
-      </c>
-      <c r="N29" s="1">
-        <v>0</v>
-      </c>
-      <c r="O29" s="1">
-        <v>0</v>
-      </c>
-      <c r="P29" s="1" t="s">
+      <c r="K29" s="4">
+        <v>0</v>
+      </c>
+      <c r="M29" s="4">
+        <v>0</v>
+      </c>
+      <c r="N29" s="4">
+        <v>0</v>
+      </c>
+      <c r="O29" s="4">
+        <v>0</v>
+      </c>
+      <c r="P29" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
+      <c r="Q29" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30" s="5">
         <v>687902</v>
       </c>
-      <c r="D30" s="2"/>
-      <c r="E30" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="2">
+      <c r="D30" s="5"/>
+      <c r="E30" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="5">
         <v>676416</v>
       </c>
-      <c r="G30" s="2">
-        <v>1</v>
-      </c>
-      <c r="H30" s="1">
+      <c r="G30" s="5">
+        <v>1</v>
+      </c>
+      <c r="H30" s="4">
         <v>2007</v>
       </c>
-      <c r="I30" s="1">
+      <c r="I30" s="4">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J30" s="4">
         <v>0.5</v>
       </c>
-      <c r="K30" s="2">
+      <c r="K30" s="5">
         <v>14543</v>
       </c>
-      <c r="L30" s="2"/>
-      <c r="M30" s="1">
+      <c r="L30" s="5"/>
+      <c r="M30" s="4">
         <v>1.9</v>
       </c>
-      <c r="N30" s="1">
+      <c r="N30" s="4">
         <v>593</v>
       </c>
-      <c r="O30" s="1">
+      <c r="O30" s="4">
         <v>596</v>
       </c>
-      <c r="P30" s="1" t="s">
+      <c r="P30" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
+      <c r="Q30" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="5">
         <v>26880</v>
       </c>
-      <c r="D31" s="2"/>
-      <c r="E31" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G31" s="1" t="s">
+      <c r="D31" s="5"/>
+      <c r="E31" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="H31" s="1">
+      <c r="H31" s="4">
         <v>1990</v>
       </c>
-      <c r="I31" s="1">
+      <c r="I31" s="4">
         <v>0.04</v>
       </c>
-      <c r="J31" s="1">
+      <c r="J31" s="4">
         <v>0.5</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="K31" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="M31" s="1">
-        <v>0</v>
-      </c>
-      <c r="N31" s="1">
-        <v>0</v>
-      </c>
-      <c r="O31" s="1">
-        <v>0</v>
-      </c>
-      <c r="P31" s="1" t="s">
+      <c r="M31" s="4">
+        <v>0</v>
+      </c>
+      <c r="N31" s="4">
+        <v>0</v>
+      </c>
+      <c r="O31" s="4">
+        <v>0</v>
+      </c>
+      <c r="P31" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
+      <c r="Q31" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C32" s="2">
+      <c r="B32" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5">
         <v>49000</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G32" s="1">
-        <v>1</v>
-      </c>
-      <c r="H32" s="1">
+      <c r="F32" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G32" s="4">
+        <v>1</v>
+      </c>
+      <c r="H32" s="4">
         <v>2008</v>
       </c>
-      <c r="I32" s="1">
+      <c r="I32" s="4">
         <v>0.12</v>
       </c>
-      <c r="J32" s="1">
+      <c r="J32" s="4">
         <v>0.5</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="M32" s="1">
+      <c r="K32" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M32" s="4">
         <v>0.3</v>
       </c>
-      <c r="N32" s="1">
+      <c r="N32" s="4">
         <v>193</v>
       </c>
-      <c r="O32" s="1">
+      <c r="O32" s="4">
         <v>194</v>
       </c>
-      <c r="P32" s="1" t="s">
+      <c r="P32" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
+      <c r="Q32" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I33" s="1">
+      <c r="B33" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I33" s="4">
         <v>0.12</v>
       </c>
-      <c r="J33" s="1">
+      <c r="J33" s="4">
         <v>0.5</v>
       </c>
-      <c r="K33" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="M33" s="1">
+      <c r="K33" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M33" s="4">
         <v>0.46</v>
       </c>
-      <c r="N33" s="2">
+      <c r="N33" s="5">
         <v>9567</v>
       </c>
-      <c r="O33" s="2">
+      <c r="O33" s="5">
         <v>9568</v>
       </c>
-      <c r="P33" s="1" t="s">
+      <c r="P33" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
+      <c r="Q33" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I34" s="1">
+      <c r="C34" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I34" s="4">
         <v>0.04</v>
       </c>
-      <c r="J34" s="1">
+      <c r="J34" s="4">
         <v>0.1</v>
       </c>
-      <c r="K34" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="M34" s="1">
+      <c r="K34" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M34" s="4">
         <v>2</v>
       </c>
-      <c r="N34" s="1">
-        <v>0</v>
-      </c>
-      <c r="O34" s="1">
+      <c r="N34" s="4">
+        <v>0</v>
+      </c>
+      <c r="O34" s="4">
         <v>2</v>
       </c>
-      <c r="P34" s="1" t="s">
+      <c r="P34" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A35" s="1" t="s">
+      <c r="Q34" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I35" s="1">
+      <c r="B35" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I35" s="4">
         <v>0.12</v>
       </c>
-      <c r="J35" s="1">
+      <c r="J35" s="4">
         <v>0.5</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="M35" s="1">
+      <c r="K35" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M35" s="4">
         <v>1.2</v>
       </c>
-      <c r="N35" s="2">
+      <c r="N35" s="5">
         <v>5265</v>
       </c>
-      <c r="O35" s="2">
+      <c r="O35" s="5">
         <v>5266</v>
       </c>
-      <c r="P35" s="1" t="s">
+      <c r="P35" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>47</v>
       </c>
@@ -2705,92 +2795,98 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
+    <row r="37" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C37" s="1">
+      <c r="C37" s="4">
         <f>AVERAGE(45095, 55832)</f>
         <v>50463.5</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="5">
         <v>44404</v>
       </c>
-      <c r="G37" s="2">
+      <c r="G37" s="5">
         <v>3</v>
       </c>
-      <c r="H37" s="1">
+      <c r="H37" s="4">
         <v>2005</v>
       </c>
-      <c r="I37" s="1">
+      <c r="I37" s="4">
         <v>0.12</v>
       </c>
-      <c r="J37" s="1">
+      <c r="J37" s="4">
         <v>0.75</v>
       </c>
-      <c r="K37" s="2">
+      <c r="K37" s="5">
         <v>1998</v>
       </c>
-      <c r="L37" s="2"/>
-      <c r="M37" s="1">
+      <c r="L37" s="5"/>
+      <c r="M37" s="4">
         <v>1.4</v>
       </c>
-      <c r="N37" s="1">
+      <c r="N37" s="4">
         <v>11</v>
       </c>
-      <c r="O37" s="1">
+      <c r="O37" s="4">
         <v>15.6</v>
       </c>
-      <c r="P37" s="1" t="s">
+      <c r="P37" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
+      <c r="Q37" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="5">
         <v>41197</v>
       </c>
-      <c r="D38" s="2"/>
-      <c r="F38" s="2">
+      <c r="D38" s="5"/>
+      <c r="F38" s="5">
         <v>41197</v>
       </c>
-      <c r="G38" s="2">
+      <c r="G38" s="5">
         <v>3</v>
       </c>
-      <c r="H38" s="1">
+      <c r="H38" s="4">
         <v>2008</v>
       </c>
-      <c r="I38" s="1">
+      <c r="I38" s="4">
         <v>0.12</v>
       </c>
-      <c r="J38" s="1">
+      <c r="J38" s="4">
         <v>0.1</v>
       </c>
-      <c r="K38" s="1">
+      <c r="K38" s="4">
         <v>247</v>
       </c>
-      <c r="M38" s="1">
+      <c r="M38" s="4">
         <v>26.2</v>
       </c>
-      <c r="N38" s="1">
+      <c r="N38" s="4">
         <v>206</v>
       </c>
-      <c r="O38" s="1">
+      <c r="O38" s="4">
         <v>233</v>
       </c>
-      <c r="P38" s="1" t="s">
+      <c r="P38" s="4" t="s">
         <v>11</v>
+      </c>
+      <c r="Q38" s="4" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
